--- a/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/Summary_Statistics.xlsx
+++ b/5_Judgemental_Nowcasts_Derivations_Analysis/0_Main_Analysis/EDA_Tables/Summary_Statistics.xlsx
@@ -609,34 +609,34 @@
         <v>18</v>
       </c>
       <c r="C5">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E5">
         <v>0.3766</v>
       </c>
       <c r="F5">
-        <v>0.9807</v>
+        <v>1.0812</v>
       </c>
       <c r="G5">
-        <v>0.6041</v>
+        <v>0.7046</v>
       </c>
       <c r="H5">
-        <v>4.7005</v>
+        <v>7.7136</v>
       </c>
       <c r="I5">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L5">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M5">
         <v>46</v>
@@ -650,37 +650,37 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0.3542</v>
+        <v>0.3907</v>
       </c>
       <c r="F6">
-        <v>0.8052</v>
+        <v>0.8086</v>
       </c>
       <c r="G6">
-        <v>0.451</v>
+        <v>0.4179</v>
       </c>
       <c r="H6">
-        <v>2.8449</v>
+        <v>2.656</v>
       </c>
       <c r="I6">
+        <v>24</v>
+      </c>
+      <c r="J6">
+        <v>7</v>
+      </c>
+      <c r="K6">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>10</v>
+      </c>
+      <c r="M6">
         <v>31</v>
-      </c>
-      <c r="J6">
-        <v>6</v>
-      </c>
-      <c r="K6">
-        <v>28</v>
-      </c>
-      <c r="L6">
-        <v>9</v>
-      </c>
-      <c r="M6">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -694,34 +694,34 @@
         <v>0</v>
       </c>
       <c r="D7">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>0.3476</v>
+      </c>
+      <c r="F7">
+        <v>1.6446</v>
+      </c>
+      <c r="G7">
+        <v>1.297</v>
+      </c>
+      <c r="H7">
+        <v>18.1661</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>10</v>
+      </c>
+      <c r="K7">
         <v>9</v>
       </c>
-      <c r="E7">
-        <v>0.469</v>
-      </c>
-      <c r="F7">
-        <v>1.7024</v>
-      </c>
-      <c r="G7">
-        <v>1.2333</v>
-      </c>
-      <c r="H7">
-        <v>12.3288</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-      <c r="J7">
-        <v>7</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
       <c r="L7">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:13">
